--- a/data_extactor/batch_10_fa/trimmed/batch_0036_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0036_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | راهبردهای یادگیری | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | راهبردهای یادگیری | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>آموزش و پرورش | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | بیان کتبی | درک کتبی | ابتکار و اصالت | روان بودن ایده‌ها</t>
+          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | بیان کتبی | درک کتبی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدرسان هنر، نمایش و موسیقی در آموزش عالی | مدرسان علوم تربیتی در آموزش عالی | معلمان دوره ابتدایی به‌استثنای آموزش استثنایی | کارشناسان برنامه‌ریزی و تدوین متون درسی | مدرسان علوم ورزشی و اوقات فراغت در آموزش عالی | دستیاران آموزشی در آموزش عالی | معلمان خصوصی و مدرسان تقویتی</t>
+          <t>مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | دستیاران آموزشی در آموزش عالی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت | راهبردهای یادگیری | نگارش | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | راهبردهای یادگیری | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و تدریس | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی</t>
+          <t>زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران و مسئولان آموزشی مدارس ابتدایی و متوسطه | معلمان دوره ابتدایی به‌استثنای آموزش استثنایی | معلمان دوره اول متوسطه به‌استثنای آموزش استثنایی و فنی و حرفه‌ای | معلمان دوره دوم متوسطه به‌استثنای آموزش استثنایی و فنی و حرفه‌ای | معلمان آموزش استثنایی دوره ابتدایی | کمک‌معلمان مدارس ابتدایی و متوسطه به‌استثنای آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
+          <t>مدیران آموزشی مقاطع ابتدایی و متوسطه | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره ابتدایی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | راهبردهای یادگیری | سخن گفتن | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نگارش | نظارت</t>
+          <t>درک مطلب | راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | آموزش و تدریس | ریاضیات | رایانه و الکترونیک | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | ریاضیات | رایانه و الکترونیک | روان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مشاوران و کارشناسان هدایت تحصیلی و شغلی | معلمان دوره ابتدایی به‌استثنای آموزش استثنایی | مدرسان علوم ریاضی در آموزش عالی | معلمان دوره اول متوسطه به‌استثنای آموزش استثنایی و فنی و حرفه‌ای | معلمان دوره دوم متوسطه به‌استثنای آموزش استثنایی و فنی و حرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | دستیاران آموزشی در آموزش عالی</t>
+          <t>مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه‌ها | روان‌شناسی | رایانه و الکترونیک | مدیریت و امور اداری</t>
+          <t>آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | ارتباطات و رسانه | روان‌شناسی | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان خصوصی و مدرسان تقویتی | معلمان حق‌التدریس و جانشین کوتاه‌مدت | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان برنامه‌ریزی و تدوین متون درسی | مربیان و استعدادیابان ورزشی</t>
+          <t>مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان خصوصی و مدرسان تقویتی | معلمان حق‌التدریس و جانشین کوتاه‌مدت | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مربیان و استعدادیابان ورزشی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تاریخ و باستان‌شناسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مدیریت و امور اداری | امور اداری و دفتری | حقوق و علوم حکومتی</t>
+          <t>تاریخ و باستان‌شناسی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | اداری | قانون و دولت</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک کتبی | انعطاف‌پذیری طبقه‌بندی | بیان شفاهی | بیان کتبی | مرتب‌سازی اطلاعات | دید نزدیک | درک شفاهی</t>
+          <t>درک کتبی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | درک شفاهی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>موزه‌داران | کارشناسان مدیریت اسناد و مدارک | متصدیان بایگانی و پرونده‌ها | تاریخ‌نگاران و پژوهشگران تاریخ | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | تکنسین‌های کتابداری | تکنسین‌ها و کارشناسان مرمت موزه</t>
+          <t>موزه‌داران | کارشناسان مدیریت اسناد و مدارک | متصدیان بایگانی و اسناد | مورخان | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | تکنسین‌های کتابداری | تکنسین‌ها و مرمت‌گران موزه</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>تاریخ و باستان‌شناسی | هنرهای تجسمی | مدیریت و امور اداری | جامعه‌شناسی و انسان‌شناسی | ارتباطات و رسانه‌ها | آموزش و تدریس</t>
+          <t>تاریخ و باستان‌شناسی | هنرهای زیبا | مدیریت و اداره | جامعه‌شناسی و انسان‌شناسی | ارتباطات و رسانه | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | دید نزدیک | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>انسان‌شناسان و باستان‌شناسان | کارشناسان اسناد و آرشیو | مدیران هنری | تاریخ‌نگاران و پژوهشگران تاریخ | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | تکنسین‌ها و کارشناسان مرمت موزه | طراحان صحنه و غرفه‌های نمایشگاهی</t>
+          <t>انسان‌شناسان و باستان‌شناسان | کارشناسان اسناد و آرشیو | مدیران هنری | مورخان | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | تکنسین‌ها و مرمت‌گران موزه | طراحان صحنه و نمایشگاه</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>هنرهای تجسمی | زبان انگلیسی | ایمنی و امنیت عمومی | تاریخ و باستان‌شناسی | مدیریت و امور اداری | شیمی</t>
+          <t>هنرهای زیبا | زبان انگلیسی | ایمنی و امنیت عمومی | تاریخ و باستان‌شناسی | مدیریت و اداره | شیمی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | مرتب‌سازی اطلاعات | پایداری دست و بازو | چابکی انگشتان | استدلال قیاسی | حساسیت به مسئله</t>
+          <t>بینایی نزدیک | درک شفاهی | ترتیب‌دهی اطلاعات | ثبات دست و بازو | مهارت انگشتان | استدلال قیاسی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارشناسان اسناد و آرشیو | تکنسین‌های شیمی | هنرمندان صنایع دستی | موزه‌داران | هنرمندان هنرهای تجسمی از جمله نقاشان، مجسمه‌سازان و تصویرگران | رنگ‌کاران و رویه‌کوبان مصنوعات چوبی | تاریخ‌نگاران و پژوهشگران تاریخ</t>
+          <t>کارشناسان اسناد و آرشیو | تکنسین‌های شیمی | هنرمندان صنایع دستی | موزه‌داران | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | مورخان</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | رایانه و الکترونیک | آموزش و تدریس | امور اداری و دفتری | ارتباطات و رسانه‌ها | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | اداری | ارتباطات و رسانه | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | مرتب‌سازی اطلاعات | انعطاف‌پذیری طبقه‌بندی | استدلال قیاسی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارشناسان اسناد و آرشیو | موزه‌داران | کارشناسان مدیریت اسناد و مدارک | متصدیان بایگانی و پرونده‌ها | کمک‌کتابداران و متصدیان دفتری کتابخانه | مدرسان علوم کتابداری و اطلاع‌رسانی در آموزش عالی | تکنسین‌های کتابداری</t>
+          <t>کارشناسان اسناد و آرشیو | موزه‌داران | کارشناسان مدیریت اسناد و مدارک | متصدیان بایگانی و اسناد | کمک‌کتابداران دفتری | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های کتابداری</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | شنیدن فعال | راهبردهای یادگیری | تفکر انتقادی</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | راهبردهای یادگیری | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | رایانه و الکترونیک | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | دید نزدیک | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارشناسان اسناد و آرشیو | کارشناسان مدیریت اسناد و مدارک | متصدیان بایگانی و پرونده‌ها | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | کمک‌کتابداران و متصدیان دفتری کتابخانه | متصدیان پذیرش و اطلاع‌رسانی | مسئولان دفاتر و منشی‌ها به‌استثنای حقوقی، پزشکی و اجرایی</t>
+          <t>کارشناسان اسناد و آرشیو | کارشناسان مدیریت اسناد و مدارک | متصدیان بایگانی و اسناد | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | کمک‌کتابداران دفتری | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری عمومی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | تولید محصولات کشاورزی و دامی | خدمات مشتریان و خدمات فردی | زیست‌شناسی | ارتباطات و رسانه‌ها | مدیریت و امور اداری</t>
+          <t>آموزش و پرورش | تولید مواد غذایی | خدمات مشتری و شخصی | زیست‌شناسی | ارتباطات و رسانه | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | مدرسان علوم کشاورزی در آموزش عالی | رابطان و مروجان سلامت جامعه | مدیران تولید کشاورزی، دامپروری و شیلات | سرپرستان کارگران کشاورزی، شیلات و جنگل‌داری | کارشناسان و مهندسان جنگل‌داری | کارشناسان علوم خاک و گیاه‌شناسی</t>
+          <t>مهندسان کشاورزی | استادان و مدرسان علوم کشاورزی در دانشگاه‌ها و مراکز آموزش عالی | رابطان سلامت و بهورزان | مدیران امور کشاورزی، دامپروری و شیلات | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | کارشناسان جنگل‌داری و جنگل‌بانان | متخصصان خاک‌شناسی و علوم گیاهی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
